--- a/每日输出/石家庄高短/石家庄-石家庄高短-每日风灵不在线.xlsx
+++ b/每日输出/石家庄高短/石家庄-石家庄高短-每日风灵不在线.xlsx
@@ -13344,7 +13344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R127"/>
+  <dimension ref="A1:R129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13445,12 +13445,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -13470,17 +13470,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>liruwei</t>
+          <t>zhangyanan</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>李如玮</t>
+          <t>张雅楠</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -13489,12 +13489,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -13508,17 +13503,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>liruwei</t>
+          <t>zhangyanan</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>李如玮</t>
+          <t>张雅楠</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -13533,7 +13528,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -13548,7 +13543,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -13558,17 +13553,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>xutiankai</t>
+          <t>yaoming01</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>许天凯</t>
+          <t>姚明</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -13577,16 +13572,11 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>11,12,13,14,15,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -13596,12 +13586,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>xutiankai</t>
+          <t>yaoming01</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>许天凯</t>
+          <t>姚明</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -13621,7 +13611,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -13636,7 +13626,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -13646,17 +13636,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>yaoming01</t>
+          <t>jiaguimin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>姚明</t>
+          <t>贾桂敏</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -13669,7 +13659,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -13679,12 +13669,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>yaoming01</t>
+          <t>jiaguimin</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>姚明</t>
+          <t>贾桂敏</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -13704,7 +13694,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -13729,17 +13719,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>新兵营烁-李智慧</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>zhangjunmei</t>
+          <t>zhengxiaomeng</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>张军妹</t>
+          <t>郑小萌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -13748,12 +13738,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -13767,12 +13752,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>zhangjunmei</t>
+          <t>zhengxiaomeng</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>张军妹</t>
+          <t>郑小萌</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -13792,7 +13777,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -13807,7 +13792,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -13817,17 +13802,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>zhangbaorui</t>
+          <t>zhangqihao01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>张宝芮</t>
+          <t>张旗号</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -13840,7 +13825,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -13850,12 +13835,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>zhangbaorui</t>
+          <t>zhangqihao01</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>张宝芮</t>
+          <t>张旗号</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -13875,7 +13860,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -13905,12 +13890,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>wangjiahe02</t>
+          <t>liuqiang</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>王佳鹤</t>
+          <t>刘强</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -13938,12 +13923,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>wangjiahe02</t>
+          <t>liuqiang</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>王佳鹤</t>
+          <t>刘强</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -13963,7 +13948,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -13993,12 +13978,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>shenmeng01</t>
+          <t>yanxuehui01</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>申萌</t>
+          <t>闫学辉</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -14007,12 +13992,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -14026,12 +14006,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>shenmeng01</t>
+          <t>yanxuehui01</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>申萌</t>
+          <t>闫学辉</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -14051,7 +14031,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -14076,17 +14056,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>heyuhan</t>
+          <t>liujinsong</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>何玉涵</t>
+          <t>刘劲松</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -14095,7 +14075,12 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -14109,12 +14094,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>heyuhan</t>
+          <t>liujinsong</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>何玉涵</t>
+          <t>刘劲松</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -14134,12 +14119,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -14149,7 +14134,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -14159,17 +14144,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>武耀巅峰-武亚伟</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ranyuyan</t>
+          <t>liujiawei</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>冉语嫣</t>
+          <t>刘佳伟</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -14182,7 +14167,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -14192,17 +14177,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ranyuyan</t>
+          <t>liujiawei</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>冉语嫣</t>
+          <t>刘佳伟</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -14217,7 +14202,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -14232,7 +14217,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -14242,17 +14227,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>新兵营烁-李智慧</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>huboyu</t>
+          <t>wangyitan</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>胡博宇</t>
+          <t>王溢潭</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -14261,11 +14246,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -14275,12 +14265,12 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>huboyu</t>
+          <t>wangyitan</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>胡博宇</t>
+          <t>王溢潭</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -14300,7 +14290,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -14325,17 +14315,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>wangrumeng</t>
+          <t>wangxuefei</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>王如梦</t>
+          <t>王雪菲</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -14344,7 +14334,12 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -14358,12 +14353,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>wangrumeng</t>
+          <t>wangxuefei</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>王如梦</t>
+          <t>王雪菲</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -14383,7 +14378,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -14408,17 +14403,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>songxiaoqiang</t>
+          <t>guoning02</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>宋晓强</t>
+          <t>郭宁</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -14441,12 +14436,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>songxiaoqiang</t>
+          <t>guoning02</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>宋晓强</t>
+          <t>郭宁</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -14466,7 +14461,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -14481,7 +14476,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -14491,17 +14486,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>新兵营烁-李智慧</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>wangsiyu07</t>
+          <t>wangdongfa</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>王思雨</t>
+          <t>王东发</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -14510,16 +14505,16 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,21,22,23</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -14529,12 +14524,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>wangsiyu07</t>
+          <t>wangdongfa</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>王思雨</t>
+          <t>王东发</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -14554,7 +14549,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -14569,7 +14564,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -14579,17 +14574,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>新兵营烁-李智慧</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>yangshimao</t>
+          <t>tianmengyang</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>杨世茂</t>
+          <t>田萌阳</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -14607,7 +14602,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -14617,12 +14612,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>yangshimao</t>
+          <t>tianmengyang</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>杨世茂</t>
+          <t>田萌阳</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -14642,12 +14637,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -14657,7 +14652,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -14667,17 +14662,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>wangjialei</t>
+          <t>liuyang06</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>王嘉磊</t>
+          <t>刘洋</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -14690,7 +14685,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -14700,17 +14695,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>wangjialei</t>
+          <t>liuyang06</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>王嘉磊</t>
+          <t>刘洋</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -14725,7 +14720,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -14755,12 +14750,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>zhangtianxiao</t>
+          <t>zhaoli</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>张天笑</t>
+          <t>赵莉</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -14769,11 +14764,11 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>0.6111111111111112</v>
+        <v>0</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>11,12,13,14,15,16,17</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -14788,12 +14783,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>zhangtianxiao</t>
+          <t>zhaoli</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>张天笑</t>
+          <t>赵莉</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -14813,7 +14808,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -14828,7 +14823,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -14838,17 +14833,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>新兵营烁-李智慧</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>zhangchao01</t>
+          <t>wangjiahe02</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>张超</t>
+          <t>王佳鹤</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -14866,7 +14861,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -14876,12 +14871,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>zhangchao01</t>
+          <t>wangjiahe02</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>张超</t>
+          <t>王佳鹤</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -14901,7 +14896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -14916,7 +14911,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -14926,17 +14921,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>武耀巅峰-武亚伟</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>yangmengjiao</t>
+          <t>yangzihan02</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>杨梦娇</t>
+          <t>杨紫涵</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -14949,7 +14944,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -14959,12 +14954,12 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>yangmengjiao</t>
+          <t>yangzihan02</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>杨梦娇</t>
+          <t>杨紫涵</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -14984,7 +14979,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -14999,7 +14994,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -15009,17 +15004,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>wanshixing</t>
+          <t>liuxulin</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>万士兴</t>
+          <t>刘旭琳</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -15032,7 +15027,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -15042,12 +15037,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>wanshixing</t>
+          <t>liuxulin</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>万士兴</t>
+          <t>刘旭琳</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -15067,7 +15062,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -15082,7 +15077,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -15092,17 +15087,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>武耀巅峰-武亚伟</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>yangzihan02</t>
+          <t>jiangzhiqiang</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>杨紫涵</t>
+          <t>姜志强</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -15115,7 +15110,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -15125,12 +15120,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>yangzihan02</t>
+          <t>jiangzhiqiang</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>杨紫涵</t>
+          <t>姜志强</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -15150,7 +15145,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -15165,7 +15160,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -15175,17 +15170,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>武耀巅峰-武亚伟</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>liweiye02</t>
+          <t>gaomingyue01</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>李伟业</t>
+          <t>高明月</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -15194,16 +15189,11 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -15213,12 +15203,12 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>liweiye02</t>
+          <t>gaomingyue01</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>李伟业</t>
+          <t>高明月</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -15238,7 +15228,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -15253,7 +15243,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -15263,17 +15253,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>yanxuehui01</t>
+          <t>houmeiting</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>闫学辉</t>
+          <t>侯梅婷</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -15286,7 +15276,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -15296,12 +15286,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>yanxuehui01</t>
+          <t>houmeiting</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>闫学辉</t>
+          <t>侯梅婷</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -15321,7 +15311,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -15336,7 +15326,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -15346,17 +15336,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>新兵营烁-李智慧</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>zhangxiaoqian01</t>
+          <t>wanghaixu</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>张晓芊</t>
+          <t>王海旭</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -15365,16 +15355,16 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>0.4444444444444444</v>
+        <v>0</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -15384,12 +15374,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>zhangxiaoqian01</t>
+          <t>wanghaixu</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>张晓芊</t>
+          <t>王海旭</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -15409,7 +15399,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -15434,17 +15424,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>liuyunbing</t>
+          <t>zhaoxicheng</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>刘云冰</t>
+          <t>赵熙呈</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -15453,12 +15443,7 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -15472,12 +15457,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>liuyunbing</t>
+          <t>zhaoxicheng</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>刘云冰</t>
+          <t>赵熙呈</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -15497,7 +15482,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -15512,7 +15497,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -15522,17 +15507,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>yangziao</t>
+          <t>wangze02</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>杨子澳</t>
+          <t>王泽</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -15541,16 +15526,11 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -15560,12 +15540,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>yangziao</t>
+          <t>wangze02</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>杨子澳</t>
+          <t>王泽</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -15585,7 +15565,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -15600,7 +15580,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -15610,17 +15590,17 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>gaomingyue01</t>
+          <t>wanglijin01</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>高明月</t>
+          <t>王立进</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -15633,7 +15613,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -15643,12 +15623,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>gaomingyue01</t>
+          <t>wanglijin01</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>高明月</t>
+          <t>王立进</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -15668,12 +15648,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -15683,7 +15663,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -15693,17 +15673,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>shangziqiang</t>
+          <t>qinxinyuan</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>商紫强</t>
+          <t>秦鑫垣</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -15712,16 +15692,16 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>21,22,23</t>
+          <t>12,13</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -15731,17 +15711,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>shangziqiang</t>
+          <t>qinxinyuan</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>商紫强</t>
+          <t>秦鑫垣</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -15756,7 +15736,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -15771,7 +15751,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -15781,17 +15761,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>jiasiwei</t>
+          <t>liuxiangyu</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>贾思薇</t>
+          <t>刘翔宇</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -15804,7 +15784,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -15814,12 +15794,12 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>jiasiwei</t>
+          <t>liuxiangyu</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>贾思薇</t>
+          <t>刘翔宇</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -15839,7 +15819,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -15854,7 +15834,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -15864,17 +15844,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>yangchenchao01</t>
+          <t>xiebofan</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>杨晨朝</t>
+          <t>解博帆</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -15883,11 +15863,16 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -15897,12 +15882,12 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>yangchenchao01</t>
+          <t>xiebofan</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>杨晨朝</t>
+          <t>解博帆</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -15922,7 +15907,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -15937,7 +15922,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -15947,17 +15932,17 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>heanqi</t>
+          <t>wangyun</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>何安琪</t>
+          <t>王云</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -15966,11 +15951,16 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -15980,12 +15970,12 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>heanqi</t>
+          <t>wangyun</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>何安琪</t>
+          <t>王云</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -16005,7 +15995,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -16035,12 +16025,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>wanghaixu</t>
+          <t>zhangxinyu</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>王海旭</t>
+          <t>张欣宇</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -16049,12 +16039,7 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -16068,12 +16053,12 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>wanghaixu</t>
+          <t>zhangxinyu</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>王海旭</t>
+          <t>张欣宇</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -16093,7 +16078,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -16123,12 +16108,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>zhengxiaomeng</t>
+          <t>qinhuile01</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>郑小萌</t>
+          <t>秦会乐</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -16137,7 +16122,12 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -16151,12 +16141,12 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>zhengxiaomeng</t>
+          <t>qinhuile01</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>郑小萌</t>
+          <t>秦会乐</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -16176,7 +16166,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -16191,7 +16181,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -16201,17 +16191,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>liruibo</t>
+          <t>zhanghui03</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>李锐博</t>
+          <t>张慧</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -16220,16 +16210,16 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -16239,12 +16229,12 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>liruibo</t>
+          <t>zhanghui03</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>李锐博</t>
+          <t>张慧</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -16264,7 +16254,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -16279,7 +16269,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -16289,17 +16279,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>guoning02</t>
+          <t>yangmengtao</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>郭宁</t>
+          <t>杨梦涛</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -16312,7 +16302,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -16322,12 +16312,12 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>guoning02</t>
+          <t>yangmengtao</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>郭宁</t>
+          <t>杨梦涛</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -16347,7 +16337,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -16362,7 +16352,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -16372,17 +16362,17 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>houmeiting</t>
+          <t>huboyu</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>侯梅婷</t>
+          <t>胡博宇</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -16395,7 +16385,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -16405,12 +16395,12 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>houmeiting</t>
+          <t>huboyu</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>侯梅婷</t>
+          <t>胡博宇</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -16430,7 +16420,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -16445,7 +16435,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -16455,17 +16445,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>chenhuanhuan01</t>
+          <t>heanqi</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>陈欢欢</t>
+          <t>何安琪</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -16474,16 +16464,11 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -16493,12 +16478,12 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>chenhuanhuan01</t>
+          <t>heanqi</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>陈欢欢</t>
+          <t>何安琪</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -16518,7 +16503,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -16533,7 +16518,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -16543,17 +16528,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>wangxuefei</t>
+          <t>liusongsong</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>王雪菲</t>
+          <t>刘松松</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -16562,16 +16547,11 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -16581,12 +16561,12 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>wangxuefei</t>
+          <t>liusongsong</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>王雪菲</t>
+          <t>刘松松</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -16606,7 +16586,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -16621,7 +16601,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -16631,17 +16611,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>liubowen02</t>
+          <t>gaoke02</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>高科</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -16650,11 +16630,16 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -16664,12 +16649,12 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>liubowen02</t>
+          <t>gaoke02</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>高科</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -16689,12 +16674,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -16704,7 +16689,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -16714,17 +16699,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>新兵营烁-李智慧</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>zhangxinyu</t>
+          <t>shijiajia</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>张欣宇</t>
+          <t>师佳佳</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -16737,7 +16722,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -16747,17 +16732,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>zhangxinyu</t>
+          <t>shijiajia</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>张欣宇</t>
+          <t>师佳佳</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -16772,7 +16757,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -16787,7 +16772,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -16797,17 +16782,17 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>yangyang04</t>
+          <t>xingaibin01</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>杨洋</t>
+          <t>邢爱斌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -16816,16 +16801,11 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -16835,12 +16815,12 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>yangyang04</t>
+          <t>xingaibin01</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>杨洋</t>
+          <t>邢爱斌</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -16860,7 +16840,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -16885,17 +16865,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>zhuhaonan</t>
+          <t>baichaoyang01</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>朱浩楠</t>
+          <t>白超洋</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -16904,11 +16884,11 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>0.6111111111111112</v>
+        <v>0</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>12,13,14,15,16,17,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -16923,12 +16903,12 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>zhuhaonan</t>
+          <t>baichaoyang01</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>朱浩楠</t>
+          <t>白超洋</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -16948,7 +16928,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -16973,17 +16953,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>lixiaoyu</t>
+          <t>liubowen02</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>李肖雨</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -17006,12 +16986,12 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>lixiaoyu</t>
+          <t>liubowen02</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>李肖雨</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -17031,12 +17011,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -17056,17 +17036,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>liuyang06</t>
+          <t>zhaojiaxin01</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>刘洋</t>
+          <t>赵佳鑫</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -17089,17 +17069,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>liuyang06</t>
+          <t>zhaojiaxin01</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>刘洋</t>
+          <t>赵佳鑫</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -17114,7 +17094,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -17129,7 +17109,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -17139,17 +17119,17 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>wangdongfa</t>
+          <t>chenhuanhuan01</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>王东发</t>
+          <t>陈欢欢</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -17158,11 +17138,16 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -17172,12 +17157,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>wangdongfa</t>
+          <t>chenhuanhuan01</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>王东发</t>
+          <t>陈欢欢</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -17197,7 +17182,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -17212,7 +17197,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -17222,17 +17207,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>jiaozehui01</t>
+          <t>wanshixing</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>焦泽晖</t>
+          <t>万士兴</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -17241,16 +17226,11 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -17260,12 +17240,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>jiaozehui01</t>
+          <t>wanshixing</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>焦泽晖</t>
+          <t>万士兴</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -17285,12 +17265,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -17300,7 +17280,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -17310,17 +17290,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>武耀巅峰-武亚伟</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>zhangwenbo01</t>
+          <t>liweiye02</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>张文博</t>
+          <t>李伟业</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -17329,16 +17309,16 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>0.3888888888888889</v>
+        <v>0</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -17348,17 +17328,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>zhangwenbo01</t>
+          <t>liweiye02</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>张文博</t>
+          <t>李伟业</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -17373,7 +17353,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -17403,12 +17383,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>liuxiaochang</t>
+          <t>gaozijia</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>刘晓畅</t>
+          <t>高紫佳</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -17431,12 +17411,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>liuxiaochang</t>
+          <t>gaozijia</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>刘晓畅</t>
+          <t>高紫佳</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -17456,7 +17436,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -17481,17 +17461,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>chenqingxian</t>
+          <t>chushengjie</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>陈庆娴</t>
+          <t>楚胜杰</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -17514,12 +17494,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>chenqingxian</t>
+          <t>chushengjie</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>陈庆娴</t>
+          <t>楚胜杰</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -17539,7 +17519,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -17554,7 +17534,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -17564,17 +17544,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>新兵营烁-李智慧</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>liuyani01</t>
+          <t>wangsiyu07</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>刘亚妮</t>
+          <t>王思雨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -17583,11 +17563,16 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -17597,12 +17582,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>liuyani01</t>
+          <t>wangsiyu07</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>刘亚妮</t>
+          <t>王思雨</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -17622,7 +17607,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -17637,7 +17622,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -17647,17 +17632,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>luyuewei</t>
+          <t>xutiankai</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>路跃威</t>
+          <t>许天凯</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -17666,16 +17651,16 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -17685,12 +17670,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>luyuewei</t>
+          <t>xutiankai</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>路跃威</t>
+          <t>许天凯</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -17710,7 +17695,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -17725,7 +17710,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -17735,17 +17720,17 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>houchaofei</t>
+          <t>liruwei</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>侯超飞</t>
+          <t>李如玮</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -17763,7 +17748,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -17773,12 +17758,12 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>houchaofei</t>
+          <t>liruwei</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>侯超飞</t>
+          <t>李如玮</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -17798,7 +17783,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -17813,7 +17798,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -17823,17 +17808,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>wangyun</t>
+          <t>chenqingxian</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>王云</t>
+          <t>陈庆娴</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -17846,7 +17831,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -17856,12 +17841,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>wangyun</t>
+          <t>chenqingxian</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>王云</t>
+          <t>陈庆娴</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -17881,7 +17866,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -17896,7 +17881,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -17906,17 +17891,17 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>pushiao</t>
+          <t>lixiaoyu</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>蒲世奥</t>
+          <t>李肖雨</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -17929,7 +17914,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -17939,12 +17924,12 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>pushiao</t>
+          <t>lixiaoyu</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>蒲世奥</t>
+          <t>李肖雨</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -17964,7 +17949,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -17979,7 +17964,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -17989,17 +17974,17 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>luxiaoping</t>
+          <t>sunjiantong01</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>卢晓萍</t>
+          <t>孙建通</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -18008,16 +17993,11 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -18027,12 +18007,12 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>luxiaoping</t>
+          <t>sunjiantong01</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>卢晓萍</t>
+          <t>孙建通</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -18052,7 +18032,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -18067,7 +18047,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -18077,17 +18057,17 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>xiaxiaoxing</t>
+          <t>chenjiabo</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>夏晓行</t>
+          <t>陈嘉博</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -18105,7 +18085,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -18115,12 +18095,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>xiaxiaoxing</t>
+          <t>chenjiabo</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>夏晓行</t>
+          <t>陈嘉博</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -18140,7 +18120,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -18170,12 +18150,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>yangmengtao</t>
+          <t>liruibo</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>杨梦涛</t>
+          <t>李锐博</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -18184,7 +18164,12 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -18198,12 +18183,12 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>yangmengtao</t>
+          <t>liruibo</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>杨梦涛</t>
+          <t>李锐博</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -18223,7 +18208,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -18253,12 +18238,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>wangyitan</t>
+          <t>lixiaoqian</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>王溢潭</t>
+          <t>李晓倩</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -18267,11 +18252,11 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -18286,12 +18271,12 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>wangyitan</t>
+          <t>lixiaoqian</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>王溢潭</t>
+          <t>李晓倩</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -18311,7 +18296,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -18326,7 +18311,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -18336,17 +18321,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>huangsixu</t>
+          <t>heyuhan</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>黄思旭</t>
+          <t>何玉涵</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -18355,16 +18340,11 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -18374,12 +18354,12 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>huangsixu</t>
+          <t>heyuhan</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>黄思旭</t>
+          <t>何玉涵</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -18399,12 +18379,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -18414,7 +18394,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -18424,17 +18404,17 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>wangyiming</t>
+          <t>zhangbeixi01</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>王义明</t>
+          <t>张倍溪</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -18447,7 +18427,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -18457,17 +18437,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>wangyiming</t>
+          <t>zhangbeixi01</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>王义明</t>
+          <t>张倍溪</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -18482,12 +18462,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -18497,7 +18477,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -18507,17 +18487,17 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>tianmengjie</t>
+          <t>shangziqiang</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>田梦洁</t>
+          <t>商紫强</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -18526,11 +18506,16 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -18540,17 +18525,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>tianmengjie</t>
+          <t>shangziqiang</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>田梦洁</t>
+          <t>商紫强</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -18565,7 +18550,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -18580,7 +18565,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -18590,17 +18575,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>zhanghui03</t>
+          <t>xiaxiaoxing</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>张慧</t>
+          <t>夏晓行</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -18609,16 +18594,16 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -18628,12 +18613,12 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>zhanghui03</t>
+          <t>xiaxiaoxing</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>张慧</t>
+          <t>夏晓行</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -18653,7 +18638,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -18678,17 +18663,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>zhaoxicheng</t>
+          <t>zhangxuanyu</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>赵熙呈</t>
+          <t>张轩瑜</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -18697,7 +18682,12 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -18711,12 +18701,12 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>zhaoxicheng</t>
+          <t>zhangxuanyu</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>赵熙呈</t>
+          <t>张轩瑜</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -18736,12 +18726,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -18751,7 +18741,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -18761,17 +18751,17 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>qinxinyuan</t>
+          <t>zhouqingyou</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>秦鑫垣</t>
+          <t>周庆有</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -18789,7 +18779,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -18799,17 +18789,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>qinxinyuan</t>
+          <t>zhouqingyou</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>秦鑫垣</t>
+          <t>周庆有</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -18824,7 +18814,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -18849,17 +18839,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>jiangzhiqiang</t>
+          <t>wuguoqiang</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>姜志强</t>
+          <t>吴国强</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -18882,12 +18872,12 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>jiangzhiqiang</t>
+          <t>wuguoqiang</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>姜志强</t>
+          <t>吴国强</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -18907,7 +18897,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -18922,7 +18912,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -18932,17 +18922,17 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>新兵营烁-李智慧</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>lixiaoqian</t>
+          <t>zhangxiaoqian01</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>李晓倩</t>
+          <t>张晓芊</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -18951,11 +18941,16 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -18965,12 +18960,12 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>lixiaoqian</t>
+          <t>zhangxiaoqian01</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>李晓倩</t>
+          <t>张晓芊</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -18990,7 +18985,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -19005,7 +19000,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -19015,17 +19010,17 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>wangzezhuang</t>
+          <t>yangmengjiao</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>王泽壮</t>
+          <t>杨梦娇</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -19034,16 +19029,11 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -19053,12 +19043,12 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>wangzezhuang</t>
+          <t>yangmengjiao</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>王泽壮</t>
+          <t>杨梦娇</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -19078,7 +19068,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -19093,7 +19083,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -19103,17 +19093,17 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>xieyulong</t>
+          <t>pushiao</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>谢宇龙</t>
+          <t>蒲世奥</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -19126,7 +19116,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -19136,12 +19126,12 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>xieyulong</t>
+          <t>pushiao</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>谢宇龙</t>
+          <t>蒲世奥</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -19161,7 +19151,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -19176,7 +19166,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -19186,17 +19176,17 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>wangyongqi01</t>
+          <t>wangzezhuang</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>王泳淇</t>
+          <t>王泽壮</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -19205,16 +19195,11 @@
         </is>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -19224,12 +19209,12 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>wangyongqi01</t>
+          <t>wangzezhuang</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>王泳淇</t>
+          <t>王泽壮</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -19249,7 +19234,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -19264,7 +19249,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -19274,17 +19259,17 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>武耀巅峰-武亚伟</t>
+          <t>新兵营烁-李智慧</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>wusiqi01</t>
+          <t>zhanghaoting</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>吴思琪</t>
+          <t>张淏婷</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -19293,16 +19278,16 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>0.8888888888888888</v>
+        <v>0</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -19312,12 +19297,12 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>wusiqi01</t>
+          <t>zhanghaoting</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>吴思琪</t>
+          <t>张淏婷</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -19337,7 +19322,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -19352,7 +19337,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -19362,17 +19347,17 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>liuyifei</t>
+          <t>zhoushijie01</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>刘逸飞</t>
+          <t>周士杰</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -19381,11 +19366,16 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -19395,12 +19385,12 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>liuyifei</t>
+          <t>zhoushijie01</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>刘逸飞</t>
+          <t>周士杰</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -19420,12 +19410,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -19445,17 +19435,17 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>liujinsong</t>
+          <t>disiyu</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>刘劲松</t>
+          <t>邸思雨</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -19483,17 +19473,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>liujinsong</t>
+          <t>disiyu</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>刘劲松</t>
+          <t>邸思雨</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -19508,7 +19498,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -19591,7 +19581,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -19606,7 +19596,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -19616,17 +19606,17 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>liuruoling</t>
+          <t>liuyaxiong</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>刘若凌</t>
+          <t>刘亚雄</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -19635,11 +19625,16 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -19649,12 +19644,12 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>liuruoling</t>
+          <t>liuyaxiong</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>刘若凌</t>
+          <t>刘亚雄</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -19674,7 +19669,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -19689,7 +19684,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -19699,17 +19694,17 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>wangzhaowei</t>
+          <t>chenhuimin01</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>王朝威</t>
+          <t>陈慧敏</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -19718,16 +19713,11 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -19737,12 +19727,12 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>wangzhaowei</t>
+          <t>chenhuimin01</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>王朝威</t>
+          <t>陈慧敏</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -19762,12 +19752,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -19787,17 +19777,17 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>kouzixuan01</t>
+          <t>ranyuyan</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>寇紫璇</t>
+          <t>冉语嫣</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -19820,17 +19810,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>kouzixuan01</t>
+          <t>ranyuyan</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>寇紫璇</t>
+          <t>冉语嫣</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -19845,7 +19835,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -19860,7 +19850,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -19870,17 +19860,17 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>gaozijia</t>
+          <t>shenmeng01</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>高紫佳</t>
+          <t>申萌</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -19889,11 +19879,16 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -19903,12 +19898,12 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>gaozijia</t>
+          <t>shenmeng01</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>高紫佳</t>
+          <t>申萌</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -19928,7 +19923,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -19953,17 +19948,17 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>武耀巅峰-武亚伟</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>yexujia</t>
+          <t>fanjiawei</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>叶旭佳</t>
+          <t>范嘉威</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -19972,11 +19967,11 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -19991,12 +19986,12 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>yexujia</t>
+          <t>fanjiawei</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>叶旭佳</t>
+          <t>范嘉威</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -20016,7 +20011,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -20031,7 +20026,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -20041,17 +20036,17 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>xingaibin01</t>
+          <t>yangziao</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>邢爱斌</t>
+          <t>杨子澳</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -20064,7 +20059,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -20074,12 +20069,12 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>xingaibin01</t>
+          <t>yangziao</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>邢爱斌</t>
+          <t>杨子澳</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -20099,7 +20094,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -20114,7 +20109,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -20124,17 +20119,17 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>gaoke02</t>
+          <t>houxinran01</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>高科</t>
+          <t>侯鑫冉</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -20147,7 +20142,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -20157,12 +20152,12 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>gaoke02</t>
+          <t>houxinran01</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>高科</t>
+          <t>侯鑫冉</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -20182,12 +20177,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -20197,7 +20192,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -20207,17 +20202,17 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>sunjiantong01</t>
+          <t>zhangwenbo01</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>孙建通</t>
+          <t>张文博</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -20230,7 +20225,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -20240,17 +20235,17 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>sunjiantong01</t>
+          <t>zhangwenbo01</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>孙建通</t>
+          <t>张文博</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -20265,7 +20260,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -20290,17 +20285,17 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>muchaopeng</t>
+          <t>luxiaoping</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>穆朝鹏</t>
+          <t>卢晓萍</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -20309,11 +20304,11 @@
         </is>
       </c>
       <c r="K82" t="n">
-        <v>0.6111111111111112</v>
+        <v>0</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -20328,12 +20323,12 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>muchaopeng</t>
+          <t>luxiaoping</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>穆朝鹏</t>
+          <t>卢晓萍</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -20353,7 +20348,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -20368,7 +20363,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -20378,17 +20373,17 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>wangjiajia02</t>
+          <t>wangjialei</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>王佳佳</t>
+          <t>王嘉磊</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -20397,16 +20392,11 @@
         </is>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -20416,12 +20406,12 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>wangjiajia02</t>
+          <t>wangjialei</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>王佳佳</t>
+          <t>王嘉磊</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -20441,7 +20431,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -20466,17 +20456,17 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>jiaguimin</t>
+          <t>zhangxingxuan</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>贾桂敏</t>
+          <t>张星玄</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -20499,12 +20489,12 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>jiaguimin</t>
+          <t>zhangxingxuan</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>贾桂敏</t>
+          <t>张星玄</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -20524,7 +20514,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -20539,7 +20529,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -20549,17 +20539,17 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>renzihan</t>
+          <t>qijingting01</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>任紫菡</t>
+          <t>祁婧婷</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -20568,16 +20558,11 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -20587,12 +20572,12 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>renzihan</t>
+          <t>qijingting01</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>任紫菡</t>
+          <t>祁婧婷</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -20612,7 +20597,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -20627,7 +20612,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -20637,17 +20622,17 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>wangze02</t>
+          <t>kouzixuan01</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>王泽</t>
+          <t>寇紫璇</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -20656,16 +20641,11 @@
         </is>
       </c>
       <c r="K86" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -20675,12 +20655,12 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>wangze02</t>
+          <t>kouzixuan01</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>王泽</t>
+          <t>寇紫璇</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -20700,7 +20680,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -20715,7 +20695,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -20725,17 +20705,17 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>tanxiaoxi</t>
+          <t>zhangchenyang</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>檀小溪</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -20753,7 +20733,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -20763,12 +20743,12 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>tanxiaoxi</t>
+          <t>zhangchenyang</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>檀小溪</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -20788,12 +20768,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -20803,7 +20783,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -20813,17 +20793,17 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>chushengjie</t>
+          <t>wangyiming</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>楚胜杰</t>
+          <t>王义明</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -20836,7 +20816,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -20846,17 +20826,17 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>chushengjie</t>
+          <t>wangyiming</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>楚胜杰</t>
+          <t>王义明</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -20871,7 +20851,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -20886,7 +20866,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -20896,17 +20876,17 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>xiebofan</t>
+          <t>liuyifei</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>解博帆</t>
+          <t>刘逸飞</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -20915,16 +20895,11 @@
         </is>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -20934,12 +20909,12 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>xiebofan</t>
+          <t>liuyifei</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>解博帆</t>
+          <t>刘逸飞</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
@@ -20959,7 +20934,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -20974,7 +20949,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -20984,17 +20959,17 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>新兵营烁-李智慧</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>zhangyachao</t>
+          <t>fengguangyuan</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>张雅超</t>
+          <t>冯光远</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -21003,16 +20978,16 @@
         </is>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -21022,12 +20997,12 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>zhangyachao</t>
+          <t>fengguangyuan</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>张雅超</t>
+          <t>冯光远</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -21047,7 +21022,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -21062,7 +21037,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -21072,17 +21047,17 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>zhangbeixi01</t>
+          <t>zhuhaonan</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>张倍溪</t>
+          <t>朱浩楠</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -21095,7 +21070,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -21105,12 +21080,12 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>zhangbeixi01</t>
+          <t>zhuhaonan</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>张倍溪</t>
+          <t>朱浩楠</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -21130,7 +21105,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -21145,7 +21120,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -21155,17 +21130,17 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>qinhuile01</t>
+          <t>wangjiajia02</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>秦会乐</t>
+          <t>王佳佳</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -21183,7 +21158,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -21193,12 +21168,12 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>qinhuile01</t>
+          <t>wangjiajia02</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>秦会乐</t>
+          <t>王佳佳</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -21218,7 +21193,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -21243,17 +21218,17 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>zhangqihao01</t>
+          <t>yangchenchao01</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>张旗号</t>
+          <t>杨晨朝</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -21276,12 +21251,12 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>zhangqihao01</t>
+          <t>yangchenchao01</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>张旗号</t>
+          <t>杨晨朝</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -21301,7 +21276,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -21326,17 +21301,17 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>zhangxingxuan</t>
+          <t>jiayunfei</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>张星玄</t>
+          <t>贾云飞</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -21345,7 +21320,12 @@
         </is>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
@@ -21359,12 +21339,12 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>zhangxingxuan</t>
+          <t>jiayunfei</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>张星玄</t>
+          <t>贾云飞</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
@@ -21384,7 +21364,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -21399,7 +21379,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -21409,17 +21389,17 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>zhoushijie01</t>
+          <t>liuruoling</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>周士杰</t>
+          <t>刘若凌</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -21428,16 +21408,11 @@
         </is>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -21447,12 +21422,12 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>zhoushijie01</t>
+          <t>liuruoling</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>周士杰</t>
+          <t>刘若凌</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -21472,12 +21447,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -21487,7 +21462,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -21497,17 +21472,17 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>zhangyu02</t>
+          <t>dongchangyiwa</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>张宇</t>
+          <t>董常依娃</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -21516,11 +21491,16 @@
         </is>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -21530,17 +21510,17 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>zhangyu02</t>
+          <t>dongchangyiwa</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>张宇</t>
+          <t>董常依娃</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -21555,7 +21535,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -21570,7 +21550,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -21580,17 +21560,17 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>新兵营烁-李智慧</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>liuxiangyu</t>
+          <t>zhangjunmei</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>刘翔宇</t>
+          <t>张军妹</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -21599,11 +21579,16 @@
         </is>
       </c>
       <c r="K97" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -21613,12 +21598,12 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>liuxiangyu</t>
+          <t>zhangjunmei</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>刘翔宇</t>
+          <t>张军妹</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
@@ -21638,7 +21623,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -21653,7 +21638,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -21663,17 +21648,17 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>huangmengya</t>
+          <t>liujiabei</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>黄梦雅</t>
+          <t>刘嘉蓓</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -21682,16 +21667,11 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -21701,12 +21681,12 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>huangmengya</t>
+          <t>liujiabei</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>黄梦雅</t>
+          <t>刘嘉蓓</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -21726,12 +21706,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -21741,7 +21721,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -21751,17 +21731,17 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>武耀巅峰-武亚伟</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>disiyu</t>
+          <t>wuyawei</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>邸思雨</t>
+          <t>武亚伟</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -21770,16 +21750,11 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -21789,17 +21764,17 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>disiyu</t>
+          <t>wuyawei</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>邸思雨</t>
+          <t>武亚伟</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -21814,7 +21789,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -21829,7 +21804,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -21839,17 +21814,17 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>新兵营烁-李智慧</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>jiayunfei</t>
+          <t>zhangyachao</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>贾云飞</t>
+          <t>张雅超</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -21867,7 +21842,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -21877,12 +21852,12 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>jiayunfei</t>
+          <t>zhangyachao</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>贾云飞</t>
+          <t>张雅超</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -21902,7 +21877,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -21917,7 +21892,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -21927,17 +21902,17 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>新兵营烁-李智慧</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>zhaojiaxin01</t>
+          <t>gaoshilun</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>赵佳鑫</t>
+          <t>高世伦</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -21946,11 +21921,16 @@
         </is>
       </c>
       <c r="K101" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -21960,12 +21940,12 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>zhaojiaxin01</t>
+          <t>gaoshilun</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>赵佳鑫</t>
+          <t>高世伦</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
@@ -21985,7 +21965,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -22010,17 +21990,17 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>zhaoli</t>
+          <t>zhangchao01</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>赵莉</t>
+          <t>张超</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -22048,12 +22028,12 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>zhaoli</t>
+          <t>zhangchao01</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>赵莉</t>
+          <t>张超</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -22073,12 +22053,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -22088,7 +22068,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -22098,17 +22078,17 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>武耀巅峰-武亚伟</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>dongchangyiwa</t>
+          <t>wusiqi01</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>董常依娃</t>
+          <t>吴思琪</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -22117,16 +22097,16 @@
         </is>
       </c>
       <c r="K103" t="n">
-        <v>0</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>9,10,11,12,15</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -22136,17 +22116,17 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>dongchangyiwa</t>
+          <t>wusiqi01</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>董常依娃</t>
+          <t>吴思琪</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -22161,7 +22141,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -22176,7 +22156,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -22186,17 +22166,17 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>武耀巅峰-武亚伟</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>wuyawei</t>
+          <t>huangsixu</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>武亚伟</t>
+          <t>黄思旭</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -22209,7 +22189,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -22219,12 +22199,12 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>wuyawei</t>
+          <t>huangsixu</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>武亚伟</t>
+          <t>黄思旭</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -22244,7 +22224,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -22259,7 +22239,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -22269,17 +22249,17 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>liushuai05</t>
+          <t>wangrumeng</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>刘帅</t>
+          <t>王如梦</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -22288,16 +22268,11 @@
         </is>
       </c>
       <c r="K105" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>16,17</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -22307,12 +22282,12 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>liushuai05</t>
+          <t>wangrumeng</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>刘帅</t>
+          <t>王如梦</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -22332,7 +22307,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -22347,7 +22322,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -22357,17 +22332,17 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>武耀巅峰-武亚伟</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>liujiawei</t>
+          <t>qinyuhao</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>刘佳伟</t>
+          <t>秦宇浩</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -22376,16 +22351,11 @@
         </is>
       </c>
       <c r="K106" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>14,15</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -22395,12 +22365,12 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>liujiawei</t>
+          <t>qinyuhao</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>刘佳伟</t>
+          <t>秦宇浩</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -22420,12 +22390,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -22445,17 +22415,17 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>zhangyanan</t>
+          <t>songxiaoqiang</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>张雅楠</t>
+          <t>宋晓强</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -22478,17 +22448,17 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>zhangyanan</t>
+          <t>songxiaoqiang</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>张雅楠</t>
+          <t>宋晓强</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -22503,7 +22473,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -22533,12 +22503,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>zhangchenyang</t>
+          <t>muchaopeng</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>穆朝鹏</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -22547,12 +22517,7 @@
         </is>
       </c>
       <c r="K108" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M108" t="inlineStr">
         <is>
@@ -22566,12 +22531,12 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>zhangchenyang</t>
+          <t>muchaopeng</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>穆朝鹏</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
@@ -22591,7 +22556,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -22606,7 +22571,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -22616,17 +22581,17 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>武耀巅峰-武亚伟</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>fanjiawei</t>
+          <t>zhangyu02</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>范嘉威</t>
+          <t>张宇</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -22635,11 +22600,16 @@
         </is>
       </c>
       <c r="K109" t="n">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,15</t>
+        </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -22649,12 +22619,12 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>fanjiawei</t>
+          <t>zhangyu02</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>范嘉威</t>
+          <t>张宇</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
@@ -22674,7 +22644,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -22689,7 +22659,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -22699,17 +22669,17 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>wuguoqiang</t>
+          <t>yangyang04</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>吴国强</t>
+          <t>杨洋</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -22718,11 +22688,16 @@
         </is>
       </c>
       <c r="K110" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -22732,12 +22707,12 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>wuguoqiang</t>
+          <t>yangyang04</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>吴国强</t>
+          <t>杨洋</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -22757,7 +22732,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -22787,12 +22762,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>maoliangliang02</t>
+          <t>jiasiwei</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>卯亮亮</t>
+          <t>贾思薇</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -22801,12 +22776,7 @@
         </is>
       </c>
       <c r="K111" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M111" t="inlineStr">
         <is>
@@ -22820,12 +22790,12 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>maoliangliang02</t>
+          <t>jiasiwei</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>卯亮亮</t>
+          <t>贾思薇</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -22845,7 +22815,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -22870,17 +22840,17 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>houxinran01</t>
+          <t>renzihan</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>侯鑫冉</t>
+          <t>任紫菡</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -22889,7 +22859,12 @@
         </is>
       </c>
       <c r="K112" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
@@ -22903,12 +22878,12 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>houxinran01</t>
+          <t>renzihan</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>侯鑫冉</t>
+          <t>任紫菡</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
@@ -22928,7 +22903,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -22943,7 +22918,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -22953,17 +22928,17 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>新兵营烁-李智慧</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>tianmengyang</t>
+          <t>yangshimao</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>田萌阳</t>
+          <t>杨世茂</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -22981,7 +22956,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -22991,12 +22966,12 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>tianmengyang</t>
+          <t>yangshimao</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>田萌阳</t>
+          <t>杨世茂</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -23016,12 +22991,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -23031,7 +23006,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -23041,17 +23016,17 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>shijiajia</t>
+          <t>maoliangliang02</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>师佳佳</t>
+          <t>卯亮亮</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -23060,11 +23035,16 @@
         </is>
       </c>
       <c r="K114" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -23074,17 +23054,17 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>shijiajia</t>
+          <t>maoliangliang02</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>师佳佳</t>
+          <t>卯亮亮</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -23099,7 +23079,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -23114,7 +23094,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -23124,17 +23104,17 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>baichaoyang01</t>
+          <t>zhangtianxiao</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>白超洋</t>
+          <t>张天笑</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -23143,16 +23123,16 @@
         </is>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -23162,12 +23142,12 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>baichaoyang01</t>
+          <t>zhangtianxiao</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>白超洋</t>
+          <t>张天笑</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
@@ -23187,7 +23167,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -23212,17 +23192,17 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>wanglijin01</t>
+          <t>jiaozehui01</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>王立进</t>
+          <t>焦泽晖</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -23231,7 +23211,12 @@
         </is>
       </c>
       <c r="K116" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
@@ -23245,12 +23230,12 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>wanglijin01</t>
+          <t>jiaozehui01</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>王立进</t>
+          <t>焦泽晖</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
@@ -23270,7 +23255,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -23285,7 +23270,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -23295,17 +23280,17 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>liusongsong</t>
+          <t>lijinru02</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>刘松松</t>
+          <t>李金儒</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -23318,7 +23303,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -23328,12 +23313,12 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>liusongsong</t>
+          <t>lijinru02</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>刘松松</t>
+          <t>李金儒</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
@@ -23353,12 +23338,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23368,7 +23353,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -23378,17 +23363,17 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>zhouqingyou</t>
+          <t>liuxiaochang</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>周庆有</t>
+          <t>刘晓畅</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -23397,16 +23382,11 @@
         </is>
       </c>
       <c r="K118" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -23416,17 +23396,17 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>zhouqingyou</t>
+          <t>liuxiaochang</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>周庆有</t>
+          <t>刘晓畅</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -23441,7 +23421,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -23456,7 +23436,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -23466,17 +23446,17 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>qijingting01</t>
+          <t>liuyani01</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>祁婧婷</t>
+          <t>刘亚妮</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -23489,7 +23469,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -23499,12 +23479,12 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>qijingting01</t>
+          <t>liuyani01</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>祁婧婷</t>
+          <t>刘亚妮</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
@@ -23524,7 +23504,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -23539,7 +23519,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -23549,17 +23529,17 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>新兵营烁-李智慧</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>liuqiang</t>
+          <t>yexujia</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>刘强</t>
+          <t>叶旭佳</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -23577,7 +23557,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -23587,12 +23567,12 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>liuqiang</t>
+          <t>yexujia</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>刘强</t>
+          <t>叶旭佳</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -23612,7 +23592,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -23627,7 +23607,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -23637,17 +23617,17 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>liujiabei</t>
+          <t>xieyulong</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>刘嘉蓓</t>
+          <t>谢宇龙</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -23660,7 +23640,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -23670,12 +23650,12 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>liujiabei</t>
+          <t>xieyulong</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>刘嘉蓓</t>
+          <t>谢宇龙</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
@@ -23695,7 +23675,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -23710,7 +23690,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -23720,17 +23700,17 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>chenhuimin01</t>
+          <t>liushuai05</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>陈慧敏</t>
+          <t>刘帅</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -23743,7 +23723,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -23753,12 +23733,12 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>chenhuimin01</t>
+          <t>liushuai05</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>陈慧敏</t>
+          <t>刘帅</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
@@ -23778,7 +23758,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -23793,7 +23773,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -23803,17 +23783,17 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>chenjiabo</t>
+          <t>luyuewei</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>陈嘉博</t>
+          <t>路跃威</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -23822,16 +23802,11 @@
         </is>
       </c>
       <c r="K123" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -23841,12 +23816,12 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>chenjiabo</t>
+          <t>luyuewei</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>陈嘉博</t>
+          <t>路跃威</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
@@ -23866,7 +23841,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -23891,17 +23866,17 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>liuyaxiong</t>
+          <t>zhangbaorui</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>刘亚雄</t>
+          <t>张宝芮</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -23910,12 +23885,7 @@
         </is>
       </c>
       <c r="K124" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M124" t="inlineStr">
         <is>
@@ -23929,12 +23899,12 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>liuyaxiong</t>
+          <t>zhangbaorui</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>刘亚雄</t>
+          <t>张宝芮</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
@@ -23954,7 +23924,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -23969,7 +23939,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -23979,17 +23949,17 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>zhangxuanyu</t>
+          <t>wangzhaowei</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>张轩瑜</t>
+          <t>王朝威</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -24007,7 +23977,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -24017,12 +23987,12 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>zhangxuanyu</t>
+          <t>wangzhaowei</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>张轩瑜</t>
+          <t>王朝威</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
@@ -24042,7 +24012,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -24057,7 +24027,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -24067,17 +24037,17 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>qinyuhao</t>
+          <t>huangmengya</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>秦宇浩</t>
+          <t>黄梦雅</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -24086,11 +24056,16 @@
         </is>
       </c>
       <c r="K126" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -24100,12 +24075,12 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>qinyuhao</t>
+          <t>huangmengya</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>秦宇浩</t>
+          <t>黄梦雅</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
@@ -24125,7 +24100,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -24140,63 +24115,244 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
+          <t>高阶三</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>骁腾问鼎-王立进</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>wangyongqi01</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>王泳淇</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>高三</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>石家庄高短</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>wangyongqi01</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>王泳淇</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>高中</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>石家庄高短</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>高阶</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
           <t>高阶一</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="F128" t="inlineStr">
         <is>
           <t>石家庄</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>继往开来-姜志强</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>fengguangyuan</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>冯光远</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>云销雨霁-姚明</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>houchaofei</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>侯超飞</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
         <is>
           <t>低价课</t>
         </is>
       </c>
-      <c r="K127" t="n">
-        <v>1</v>
-      </c>
-      <c r="M127" t="inlineStr">
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t>高一</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr">
-        <is>
-          <t>石家庄高短</t>
-        </is>
-      </c>
-      <c r="O127" t="inlineStr">
-        <is>
-          <t>fengguangyuan</t>
-        </is>
-      </c>
-      <c r="P127" t="inlineStr">
-        <is>
-          <t>冯光远</t>
-        </is>
-      </c>
-      <c r="Q127" t="inlineStr">
-        <is>
-          <t>高中</t>
-        </is>
-      </c>
-      <c r="R127" t="inlineStr">
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>石家庄高短</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>houchaofei</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>侯超飞</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>高中</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>石家庄高短</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>高阶</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>高阶二</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>破浪前行-陈嘉博</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>tanxiaoxi</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>檀小溪</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>石家庄高短</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>tanxiaoxi</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>檀小溪</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>高中</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
         <is>
           <t>石家庄高短</t>
         </is>
@@ -24213,7 +24369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -24380,17 +24536,17 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>杨世茂</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>0</v>
+          <t>李晓倩</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0</v>
+        <v>0.3888888888888889</v>
       </c>
     </row>
     <row r="7">
@@ -24411,7 +24567,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>王佳鹤</t>
+          <t>杨世茂</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
@@ -24442,7 +24598,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>王思雨</t>
+          <t>王佳鹤</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
@@ -24473,7 +24629,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>王海旭</t>
+          <t>王思雨</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
@@ -24504,7 +24660,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>王溢潭</t>
+          <t>王海旭</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
@@ -24530,12 +24686,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>新兵营烁-李智慧</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>刘亚雄</t>
+          <t>王溢潭</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
@@ -24566,11 +24722,11 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>周士杰</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>1</v>
+          <t>刘亚雄</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>1</v>
@@ -24597,11 +24753,11 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>陈欢欢</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>0</v>
+          <t>周士杰</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>1</v>
@@ -24623,22 +24779,22 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>刘帅</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>1</v>
+          <t>陈欢欢</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.8888888888888888</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -24669,7 +24825,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0</v>
+        <v>0.6111111111111112</v>
       </c>
     </row>
     <row r="16">
@@ -24886,7 +25042,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="23">
@@ -24947,8 +25103,8 @@
       <c r="F24" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="6" t="n">
-        <v>1</v>
+      <c r="G24" s="5" t="n">
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="25">
@@ -25041,7 +25197,7 @@
         <v>1</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="28">
@@ -25088,22 +25244,22 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>黄思旭</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>0.9444444444444444</v>
+          <t>刘云冰</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="G29" s="3" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="30">
@@ -25124,17 +25280,17 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>刘云冰</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>0.3888888888888889</v>
+          <t>张晨阳</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.3888888888888889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -25155,17 +25311,17 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>张晨阳</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="n">
-        <v>1</v>
+          <t>朱浩楠</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0.5555555555555556</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G31" s="5" t="n">
-        <v>0</v>
+      <c r="G31" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -25186,17 +25342,17 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>朱浩楠</t>
+          <t>王泽壮</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -25217,17 +25373,17 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>杨子澳</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="n">
-        <v>1</v>
+          <t>穆朝鹏</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0.6111111111111112</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G33" s="5" t="n">
-        <v>0.5555555555555556</v>
+      <c r="G33" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -25243,22 +25399,22 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>王泽壮</t>
+          <t>冯光远</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>0</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.9444444444444444</v>
       </c>
     </row>
     <row r="35">
@@ -25274,22 +25430,22 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>穆朝鹏</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>0.6111111111111112</v>
+          <t>张宇</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="36">
@@ -25305,12 +25461,12 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>路跃威</t>
+          <t>高科</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
@@ -25331,27 +25487,27 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>武耀巅峰-武亚伟</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>冯光远</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>0.8888888888888888</v>
+          <t>吴思琪</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G37" s="6" t="n">
-        <v>1</v>
+      <c r="G37" s="5" t="n">
+        <v>0.7222222222222222</v>
       </c>
     </row>
     <row r="38">
@@ -25372,7 +25528,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>刘佳伟</t>
+          <t>李伟业</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
@@ -25382,7 +25538,7 @@
         <v>1</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.8888888888888888</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -25403,7 +25559,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>吴思琪</t>
+          <t>范嘉威</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
@@ -25413,7 +25569,7 @@
         <v>1</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="40">
@@ -25429,12 +25585,12 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>武耀巅峰-武亚伟</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>李伟业</t>
+          <t>卯亮亮</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
@@ -25465,7 +25621,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>卯亮亮</t>
+          <t>张晓芊</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
@@ -25475,7 +25631,7 @@
         <v>1</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0</v>
+        <v>0.9444444444444444</v>
       </c>
     </row>
     <row r="42">
@@ -25496,7 +25652,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>张晓芊</t>
+          <t>杨洋</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
@@ -25506,7 +25662,7 @@
         <v>1</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.4444444444444444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -25527,7 +25683,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>杨洋</t>
+          <t>焦泽晖</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
@@ -25553,16 +25709,16 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>焦泽晖</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="n">
-        <v>1</v>
+          <t>叶旭佳</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0.5555555555555556</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>1</v>
@@ -25589,11 +25745,11 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>叶旭佳</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="n">
-        <v>0.5555555555555556</v>
+          <t>王佳佳</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>1</v>
@@ -25620,7 +25776,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>王佳佳</t>
+          <t>王朝威</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
@@ -25651,7 +25807,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>王朝威</t>
+          <t>王泳淇</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
@@ -25682,17 +25838,17 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>王泳淇</t>
+          <t>王立进</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F48" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="5" t="n">
+      <c r="F48" s="5" t="n">
         <v>0</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -25713,7 +25869,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>王泽</t>
+          <t>黄梦雅</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
@@ -25723,7 +25879,7 @@
         <v>1</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -25734,27 +25890,27 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>王立进</t>
+          <t>张慧</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="6" t="n">
-        <v>1</v>
+      <c r="F50" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.2222222222222222</v>
       </c>
     </row>
     <row r="51">
@@ -25765,17 +25921,17 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>黄梦雅</t>
+          <t>王云</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
@@ -25785,7 +25941,7 @@
         <v>1</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0</v>
+        <v>0.9444444444444444</v>
       </c>
     </row>
     <row r="52">
@@ -25806,7 +25962,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>张慧</t>
+          <t>王雪菲</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
@@ -25837,17 +25993,17 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>王雪菲</t>
+          <t>许天凯</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F53" s="6" t="n">
-        <v>1</v>
+      <c r="F53" s="5" t="n">
+        <v>0.5555555555555556</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="54">
@@ -25868,17 +26024,17 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>许天凯</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>0.5555555555555556</v>
+          <t>贾云飞</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -25899,17 +26055,17 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>贾云飞</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="F55" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>0</v>
+          <t>贾桂敏</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -25925,22 +26081,22 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>贾桂敏</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F56" s="5" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="G56" s="6" t="n">
-        <v>1</v>
+          <t>刘劲松</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -25961,11 +26117,11 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>刘劲松</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>0.8888888888888888</v>
+          <t>张超</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>1</v>
@@ -25992,7 +26148,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>张超</t>
+          <t>李如玮</t>
         </is>
       </c>
       <c r="E58" s="6" t="n">
@@ -26018,12 +26174,12 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>李如玮</t>
+          <t>任紫菡</t>
         </is>
       </c>
       <c r="E59" s="6" t="n">
@@ -26054,17 +26210,17 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>任紫菡</t>
+          <t>侯梅婷</t>
         </is>
       </c>
       <c r="E60" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F60" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>0</v>
+      <c r="F60" s="5" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -26085,17 +26241,17 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>侯梅婷</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F61" s="5" t="n">
+          <t>张天笑</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n">
         <v>0.6111111111111112</v>
       </c>
-      <c r="G61" s="6" t="n">
-        <v>1</v>
+      <c r="F61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="62">
@@ -26116,17 +26272,17 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>张天笑</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>0.6111111111111112</v>
+          <t>檀小溪</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.6111111111111112</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -26147,14 +26303,14 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>檀小溪</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" s="6" t="n">
-        <v>1</v>
+          <t>田萌阳</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G63" s="5" t="n">
         <v>0</v>
@@ -26178,14 +26334,14 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>田萌阳</t>
+          <t>解博帆</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G64" s="5" t="n">
         <v>0</v>
@@ -26209,14 +26365,14 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>解博帆</t>
+          <t>赵莉</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="F65" s="5" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G65" s="5" t="n">
         <v>0</v>
@@ -26240,14 +26396,14 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>赵莉</t>
+          <t>陈嘉博</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="F66" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G66" s="5" t="n">
         <v>0</v>
@@ -26266,19 +26422,19 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>陈嘉博</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="5" t="n">
-        <v>0</v>
+          <t>周庆有</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G67" s="5" t="n">
         <v>0</v>
@@ -26302,7 +26458,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>周庆有</t>
+          <t>商紫强</t>
         </is>
       </c>
       <c r="E68" s="6" t="n">
@@ -26312,7 +26468,7 @@
         <v>1</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0</v>
+        <v>0.9444444444444444</v>
       </c>
     </row>
     <row r="69">
@@ -26333,7 +26489,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>商紫强</t>
+          <t>董常依娃</t>
         </is>
       </c>
       <c r="E69" s="6" t="n">
@@ -26343,7 +26499,7 @@
         <v>1</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -26364,7 +26520,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>张文博</t>
+          <t>邸思雨</t>
         </is>
       </c>
       <c r="E70" s="6" t="n">
@@ -26374,68 +26530,6 @@
         <v>1</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.3888888888888889</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>石家庄高短</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>高二</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>紫翼飞腾-商紫强</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>董常依娃</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F71" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>石家庄高短</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>高二</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>紫翼飞腾-商紫强</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t>邸思雨</t>
-        </is>
-      </c>
-      <c r="E72" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F72" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" s="5" t="n">
         <v>0</v>
       </c>
     </row>
